--- a/docs/таблицы карт/КАРТЫ — свод 1.49.0.xlsx
+++ b/docs/таблицы карт/КАРТЫ — свод 1.49.0.xlsx
@@ -1386,7 +1386,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2 СПЕЦ-ДЕЙСТВИЯ</t>
+          <t xml:space="preserve">+1 СПЕЦ-ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{amount=2, free=true}</t>
+          <t xml:space="preserve">{amount=1, free=true}</t>
         </is>
       </c>
       <c r="E10" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2 СПЕЦ-ДЕЙСТВИЯ</t>
+          <t xml:space="preserve">+1 СПЕЦ-ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2 СПЕЦ-ДЕЙСТВИЯ</t>
+          <t xml:space="preserve">+1 СПЕЦ-ДЕЙСТВИЕ</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
